--- a/reports/feature_inventory.xlsx
+++ b/reports/feature_inventory.xlsx
@@ -8956,7 +8956,7 @@
     <t xml:space="preserve">Iteration 73 (steadier screen, on the 853): beside form lines and connection windows +0.0017 (+0.0003 to +0.0033), resolved worse, the outsiders +0.0074: the third pedigree reading to fail. Retired.</t>
   </si>
   <si>
-    <t xml:space="preserve">Iteration 75 (screen): -0.0011, unresolved; maiden, novice and bumper races -0.0048. Iteration 80 (served recipe, Huber): -0.0032 beside the 958h, those races -0.0067. Iteration 81 (served recipe, squared error): -0.0018 (-0.0028 to -0.0008) beside the 958, concordance resolved better. In the 968, the next candidate (train-bfsp run 41; its Huber twin run 42).</t>
+    <t xml:space="preserve">Iteration 75 (screen): -0.0011, unresolved; maiden, novice and bumper races -0.0048. Iteration 80 (served recipe, Huber): -0.0032 beside the 958h, those races -0.0067. Iteration 81 (served recipe, squared error): -0.0018 (-0.0028 to -0.0008) beside the 958, concordance resolved better. In the 968, the next candidate (train-bfsp run 41: verify PASS, parity clean, every feature identical on the 06:00 card; its Huber twin run 42).</t>
   </si>
   <si>
     <t xml:space="preserve">Iteration 69 (steadier screen, on the 853): -0.0056 (-0.0072 to -0.0041) alone, but beside form lines and connection windows -0.0008 (-0.0021 to +0.0005), unresolved, the early-price rule +7.84% against +8.47%: what it reads, connection windows already carry. Retired.</t>
@@ -8971,7 +8971,7 @@
     <t xml:space="preserve">Built 26 Sep beside the debut market block: the engine reads the pedigree only by results. Iteration 84 (the 968 + the block, two seeds each, served recipe) queued.</t>
   </si>
   <si>
-    <t xml:space="preserve">Built 26 Sep from a table of every horse's runs before 2021 (114,078 horses, 1.31m runs): 74% of 2021's runs, 47% of 2022's and 8% of the development window's have such a record. Iteration 83 (the 958 + the block, served recipe) under test.</t>
+    <t xml:space="preserve">Built 26 Sep from a table of every horse's runs before 2021 (114,078 horses, 1.31m runs): 74% of 2021's runs, 47% of 2022's and 8% of the development window's have such a record. Iteration 83 (the 958 + the block, served recipe): against four refits of the 958 -0.0008 to +0.0002; on the 4,330 runners with a pre-2021 record +0.0010. Retired.</t>
   </si>
   <si>
     <t xml:space="preserve">Iteration 35: -0.0004; iteration 54 (steadier screen): -0.0009 (-0.0023 to +0.0003): nothing.</t>

--- a/reports/feature_inventory.xlsx
+++ b/reports/feature_inventory.xlsx
@@ -8968,7 +8968,7 @@
     <t xml:space="preserve">Iteration 44: +0.0007 (-0.0009 to +0.0022), the outsiders worse: the trees already read these measures against the field. Retired.</t>
   </si>
   <si>
-    <t xml:space="preserve">Built 26 Sep beside the debut market block: the engine reads the pedigree only by results. Iteration 84 (the 968 + the block, two seeds each, served recipe) queued.</t>
+    <t xml:space="preserve">Built 26 Sep beside the debut market block: the engine reads the pedigree only by results. Iteration 84 (the 968 + the block, two seeds each, served recipe): the averages -0.0006 (-0.0012 to -0.0000), maiden/novice/bumper races -0.0012 unresolved; the early-price rule lower in every reading (+9.26% against +9.66%). Retired.</t>
   </si>
   <si>
     <t xml:space="preserve">Built 26 Sep from a table of every horse's runs before 2021 (114,078 horses, 1.31m runs): 74% of 2021's runs, 47% of 2022's and 8% of the development window's have such a record. Iteration 83 (the 958 + the block, served recipe): against four refits of the 958 -0.0008 to +0.0002; on the 4,330 runners with a pre-2021 record +0.0010. Retired.</t>

--- a/reports/feature_inventory.xlsx
+++ b/reports/feature_inventory.xlsx
@@ -9547,13 +9547,13 @@
     <t xml:space="preserve">Built 26 Sep from a table of every horse's runs before 2021 (114,078 horses, 1.31m runs): 74% of 2021's runs, 47% of 2022's and 8% of the development window's have such a record. Iteration 83 (the 958 + the block, served recipe): against four refits of the 958 -0.0008 to +0.0002; on the 4,330 runners with a pre-2021 record +0.0010. Retired.</t>
   </si>
   <si>
-    <t xml:space="preserve">Built 27 Sep from model/state_space.py, strictly from earlier days. Screened against the pair's errors (research/queries/travel_residuals.py): -3.89 x 10^-4 jointly (-6.12 to -1.64), the rating's uncertainty and its gap to today's mark the strongest cells. Iteration 96 fits it on the 968s5xh's recipe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built 27 Sep from model/handicap_features.py, last runs on earlier days only. Screened: -2.31 x 10^-4 jointly (-3.98 to -0.51). Iteration 96 fits it with the Kalman rating.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built 27 Sep with coordinates for the 86 British and Irish courses. Screened: -1.45 x 10^-4 jointly (-3.36 to +0.52), unresolved; maidens, novices and bumpers -4.08 and Irish courses -5.28, both resolved; the yard's share of runners at the course -1.19 alone. Iteration 96 fits it alone and with the other two.</t>
+    <t xml:space="preserve">Built 27 Sep from model/state_space.py, strictly from earlier days; parity clean at 06:00. Screened against the pair's errors: -3.89 x 10^-4 jointly, but iteration 96 fitted it with the handicap angles on the 968s5xh at -0.0002 (Brier skill resolved worse); beside travel about -0.0005, within the refit noise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 27 Sep from model/handicap_features.py, last runs on earlier days only; parity clean. Screened -2.31 x 10^-4; fitted with the Kalman rating on the 968s5xh: -0.0002 (iteration 96), nothing alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 27 Sep with coordinates for the 86 British and Irish courses; parity clean at 06:00. The screen read it weakly (-1.45 x 10^-4, unresolved; maidens, novices and bumpers -4.08, Irish courses -5.28), but iteration 96 fitted it on the 968s5xh at -0.0012 (-0.0018 to -0.0005), maidens, novices and bumpers -0.0025; with the Kalman rating and handicap angles -0.0017 (-0.0024 to -0.0011), Brier skill and concordance level, the rule unchanged; beside the within-race partner the pair 0.3970 against 0.3981. Iteration 97 fits the partner with it.</t>
   </si>
   <si>
     <t xml:space="preserve">Iteration 35: -0.0004; iteration 54 (steadier screen): -0.0009 (-0.0023 to +0.0003): nothing.</t>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">COUNTIF(Features!$F$2:$F$1462,A6)</f>
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="B7" s="4" t="n">
         <f aca="false">COUNTIF(Features!$F$2:$F$1462,A7)</f>
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -55807,7 +55807,7 @@
         <v>2900</v>
       </c>
       <c r="F1361" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1361" s="8"/>
       <c r="H1361" s="6" t="str">
@@ -55839,7 +55839,7 @@
         <v>2900</v>
       </c>
       <c r="F1362" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1362" s="8"/>
       <c r="H1362" s="6" t="str">
@@ -55871,7 +55871,7 @@
         <v>2900</v>
       </c>
       <c r="F1363" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1363" s="8"/>
       <c r="H1363" s="6" t="str">
@@ -55903,7 +55903,7 @@
         <v>2900</v>
       </c>
       <c r="F1364" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1364" s="8"/>
       <c r="H1364" s="6" t="str">
@@ -55935,7 +55935,7 @@
         <v>2900</v>
       </c>
       <c r="F1365" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1365" s="8"/>
       <c r="H1365" s="6" t="str">
@@ -55967,7 +55967,7 @@
         <v>2900</v>
       </c>
       <c r="F1366" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1366" s="8"/>
       <c r="H1366" s="6" t="str">
@@ -55999,7 +55999,7 @@
         <v>2900</v>
       </c>
       <c r="F1367" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1367" s="8"/>
       <c r="H1367" s="6" t="str">
@@ -56031,7 +56031,7 @@
         <v>2900</v>
       </c>
       <c r="F1368" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1368" s="8"/>
       <c r="H1368" s="6" t="str">
@@ -56063,7 +56063,7 @@
         <v>2900</v>
       </c>
       <c r="F1369" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1369" s="8"/>
       <c r="H1369" s="6" t="str">
@@ -60153,7 +60153,7 @@
         <v>2897</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="4" t="n">
         <f aca="false">COUNTIFS(Features!$B$2:$B$1462,A42)</f>

--- a/reports/feature_inventory.xlsx
+++ b/reports/feature_inventory.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10784" uniqueCount="3358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10784" uniqueCount="3359">
   <si>
     <t xml:space="preserve">Ashcroft price model: feature inventory</t>
   </si>
@@ -9811,187 +9811,190 @@
     <t xml:space="preserve">Lengths beaten per place behind the winner (how strung out the field was)</t>
   </si>
   <si>
+    <t xml:space="preserve">Screened (research query misc_residuals, 27 Sep, x 10^-4 on the pair's mean |log error|): the last race's lengths per place and the horse's lengths against it +0.66 jointly, nothing. Not built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing-sectional proxy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed over the final furlongs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No sectional or per-horse times in the data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headgear type flags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One flag per headgear item (blinkers, visor, cheekpieces, hood, tongue-tie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial: one category column. Screened (research query misc_residuals, 27 Sep, x 10^-4 on the pair's mean |log error|): each item worn, the number worn and headgear taken off -0.98 jointly (-2.23 to +0.24), unresolved; the items alone -0.76, resolved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age restriction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Race conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age band of the race (2yo, 3yo only, 3yo+, 4yo+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">race_restrictions_age is never read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claimer flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whether the jockey claims an allowance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial: raw claim only; is_claimer is opt-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR percentile in the field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official rating's percentile within the race</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial: difference to the max and median only. Screened (research query misc_residuals, 27 Sep, x 10^-4 on the pair's mean |log error|) with the rating ladder: nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR trajectory slope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slope of the official rating over recent runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial: changes only. Screened (research query misc_residuals, 27 Sep, x 10^-4 on the pair's mean |log error|): the rating's slope over three runs and against its peak, with the class ladder, -0.85 jointly (-2.33 to +0.55), unresolved; against the peak alone -0.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month / season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonal effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surveyed on 24 Sep: nothing for the price to miss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day of week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekday effects (strength of meetings)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surveyed: nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run number within the current campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written in model/primitives.py, never called; fr_runs_since_break now covers most of it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Major-race experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runs and form in Group / Listed / major races</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screened 27 Sep against the best model's errors (black-type runs, finishing position and win rate before today: +0.53 x 10^-4, nothing; research/queries/travel_residuals.py)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class ladder vs career median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today's class against the horse's career median class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial: against a three-run mean. Screened (research query misc_residuals, 27 Sep, x 10^-4 on the pair's mean |log error|) against the median and best class: nothing (against the best +0.91, worse)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class x speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed figures scaled by the class they were run in</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not built</t>
   </si>
   <si>
-    <t xml:space="preserve">B4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing-sectional proxy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed over the final furlongs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No sectional or per-horse times in the data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Headgear type flags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One flag per headgear item (blinkers, visor, cheekpieces, hood, tongue-tie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial: one category column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age restriction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Race conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age band of the race (2yo, 3yo only, 3yo+, 4yo+)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">race_restrictions_age is never read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claimer flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether the jockey claims an allowance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial: raw claim only; is_claimer is opt-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR percentile in the field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Official rating's percentile within the race</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial: difference to the max and median only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR trajectory slope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slope of the official rating over recent runs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial: changes only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Month / season</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Context</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seasonal effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surveyed on 24 Sep: nothing for the price to miss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day of week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekday effects (strength of meetings)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surveyed: nothing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign stage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run number within the current campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Written in model/primitives.py, never called; fr_runs_since_break now covers most of it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Major-race experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Runs and form in Group / Listed / major races</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screened 27 Sep against the best model's errors (black-type runs, finishing position and win rate before today: +0.53 x 10^-4, nothing; research/queries/travel_residuals.py)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Class ladder vs career median</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Today's class against the horse's career median class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial: against a three-run mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Class x speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed figures scaled by the class they were run in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight per OR point</t>
+    <t xml:space="preserve">L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight against the last three runs</t>
   </si>
   <si>
     <t xml:space="preserve">Handicap</t>
   </si>
   <si>
-    <t xml:space="preserve">Weight carried relative to the official rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The handicap block's hc_wt_vs_mark is close (opt-in, added nothing against the result)</t>
+    <t xml:space="preserve">Weight carried today less the mean of its last three runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screened (research query misc_residuals, 27 Sep, x 10^-4 on the pair's mean |log error|): -2.14 (-3.64 to -0.62), resolved, the size of the handicap angles' read; the model reads the weight against the last run (weight_change_lr) only. The next small candidate for a fit</t>
   </si>
   <si>
     <t xml:space="preserve">R1</t>
@@ -10765,7 +10768,7 @@
       </c>
       <c r="B16" s="4" t="n">
         <f aca="false">COUNTIF('Not yet developed'!$G$2:$G$27,A16)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -10776,7 +10779,7 @@
       </c>
       <c r="B17" s="4" t="n">
         <f aca="false">COUNTIF('Not yet developed'!$G$2:$G$27,A17)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -61943,7 +61946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
         <v>3243</v>
       </c>
@@ -61963,7 +61966,7 @@
         <v>3246</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61989,7 +61992,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>3252</v>
       </c>
@@ -62058,7 +62061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
         <v>3267</v>
       </c>
@@ -62081,7 +62084,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>3272</v>
       </c>
@@ -62196,7 +62199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>3294</v>
       </c>
@@ -62236,30 +62239,30 @@
         <v>3241</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>3246</v>
+        <v>3302</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>3305</v>
+        <v>3306</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>3241</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>3306</v>
+        <v>3307</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>14</v>
@@ -62267,22 +62270,22 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>3264</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>3241</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>15</v>
@@ -62290,22 +62293,22 @@
     </row>
     <row r="18" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>3312</v>
+        <v>3313</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>3314</v>
+        <v>3315</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>3241</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>3315</v>
+        <v>3316</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>15</v>
@@ -62313,22 +62316,22 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>3317</v>
+        <v>3318</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>3318</v>
+        <v>3319</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>15</v>
@@ -62336,22 +62339,22 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>3325</v>
+        <v>3326</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>3241</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>14</v>
@@ -62359,22 +62362,22 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>3327</v>
+        <v>3328</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>3264</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>3250</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>16</v>
@@ -62382,22 +62385,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>3331</v>
+        <v>3332</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>3334</v>
+        <v>3335</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>15</v>
@@ -62405,22 +62408,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>15</v>
@@ -62428,22 +62431,22 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>15</v>
@@ -62451,22 +62454,22 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>3345</v>
+        <v>3346</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>14</v>
@@ -62474,22 +62477,22 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>15</v>
@@ -62497,22 +62500,22 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>3356</v>
+        <v>3357</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>17</v>

--- a/reports/feature_inventory.xlsx
+++ b/reports/feature_inventory.xlsx
@@ -9652,10 +9652,10 @@
     <t xml:space="preserve">Built 27 Sep with coordinates for the 86 British and Irish courses; parity clean at 06:00. The screen read it weakly, the fits carried it: on the 968s5xh -0.0012 (-0.0018 to -0.0005), with the Kalman rating and handicap angles -0.0017 (seed 42) and -0.0011 (seed 7); the within-race partner with travel -0.0010, with all three -0.0014 (iteration 97). The pair of the two with all three prices 0.3966 against 0.3981, concordance resolved better: the recommendation, in training for serving (train-bfsp runs 52 and 53).</t>
   </si>
   <si>
-    <t xml:space="preserve">Built 28 Sep: the industry SP (odds, net) against the Betfair SP, and the Betfair place SP against the win SP, in past runs, each against its price band, field size and code or places paid on earlier days; the horse's, its yard's and its rider's. A residual screen could not say whether it adds (research query run 36360636883 reads features the model already holds as strongly as new ones); iteration 98 fits it on the 968s5xh with the three blocks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built 28 Sep: the horse's finishing position and its yard's A-E against the Betfair SP in today's month and the month either side, 300 days back or more. Iteration 98 fits it with market history.</t>
+    <t xml:space="preserve">Built 28 Sep: the industry SP (odds, net) against the Betfair SP, and the Betfair place SP against the win SP, in past runs, each against its price band, field size and code or places paid on earlier days; the horse's, its yard's and its rider's. Iteration 98, on the 968s5xh with the three blocks: +0.0006 (+0.0000 to +0.0012), resolved worse at the edge; beside the partner +0.0003 against the candidate pair. The rule +10.33% and the top pick +1.66% against +10.16% and +1.57%, inside their noise. Retired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 28 Sep: the horse's finishing position and its yard's A-E against the Betfair SP in today's month and the month either side, 300 days back or more. Iteration 98, with market history: -0.0000 alone, -0.0002 (-0.0005 to +0.0001) in the pair with its concordance resolved worse (-0.0011). Retired.</t>
   </si>
   <si>
     <t xml:space="preserve">Iteration 35: -0.0004; iteration 54 (steadier screen): -0.0009 (-0.0023 to +0.0003): nothing.</t>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">COUNTIF(Features!$F$2:$F$1475,A6)</f>
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B7" s="4" t="n">
         <f aca="false">COUNTIF(Features!$F$2:$F$1475,A7)</f>
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -56938,7 +56938,7 @@
         <v>2921</v>
       </c>
       <c r="F1370" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1370" s="8"/>
       <c r="H1370" s="6" t="str">
@@ -56970,7 +56970,7 @@
         <v>2921</v>
       </c>
       <c r="F1371" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1371" s="8"/>
       <c r="H1371" s="6" t="str">
@@ -57002,7 +57002,7 @@
         <v>2921</v>
       </c>
       <c r="F1372" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1372" s="8"/>
       <c r="H1372" s="6" t="str">
@@ -57034,7 +57034,7 @@
         <v>2921</v>
       </c>
       <c r="F1373" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1373" s="8"/>
       <c r="H1373" s="6" t="str">
@@ -57066,7 +57066,7 @@
         <v>2921</v>
       </c>
       <c r="F1374" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1374" s="8"/>
       <c r="H1374" s="6" t="str">
@@ -57098,7 +57098,7 @@
         <v>2921</v>
       </c>
       <c r="F1375" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1375" s="8"/>
       <c r="H1375" s="6" t="str">
@@ -57130,7 +57130,7 @@
         <v>2921</v>
       </c>
       <c r="F1376" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1376" s="8"/>
       <c r="H1376" s="6" t="str">
@@ -57162,7 +57162,7 @@
         <v>2921</v>
       </c>
       <c r="F1377" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1377" s="8"/>
       <c r="H1377" s="6" t="str">
@@ -57194,7 +57194,7 @@
         <v>2940</v>
       </c>
       <c r="F1378" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1378" s="8"/>
       <c r="H1378" s="6" t="str">
@@ -57226,7 +57226,7 @@
         <v>2940</v>
       </c>
       <c r="F1379" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1379" s="8"/>
       <c r="H1379" s="6" t="str">
@@ -57258,7 +57258,7 @@
         <v>2940</v>
       </c>
       <c r="F1380" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1380" s="8"/>
       <c r="H1380" s="6" t="str">
@@ -57290,7 +57290,7 @@
         <v>2940</v>
       </c>
       <c r="F1381" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1381" s="8"/>
       <c r="H1381" s="6" t="str">
@@ -57322,7 +57322,7 @@
         <v>2940</v>
       </c>
       <c r="F1382" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1382" s="8"/>
       <c r="H1382" s="6" t="str">
@@ -61438,7 +61438,7 @@
         <v>2918</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" s="4" t="n">
         <f aca="false">COUNTIFS(Features!$B$2:$B$1475,A43)</f>
@@ -61464,7 +61464,7 @@
         <v>2937</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" s="4" t="n">
         <f aca="false">COUNTIFS(Features!$B$2:$B$1475,A44)</f>

--- a/reports/feature_inventory.xlsx
+++ b/reports/feature_inventory.xlsx
@@ -9901,7 +9901,7 @@
     <t xml:space="preserve">Built 28 Sep: the horse's finishing position and its yard's A-E against the Betfair SP in today's month and the month either side, 300 days back or more. Iteration 98, with market history: -0.0000 alone, -0.0002 (-0.0005 to +0.0001) in the pair with its concordance resolved worse (-0.0011). Retired.</t>
   </si>
   <si>
-    <t xml:space="preserve">Built 30 Sep at the owner's ask (measures from the financial markets): the Sharpe ratio of level-stake returns at the Betfair SP, the signed chi (z-score) of winners against the prices' expectation and A/E for the trainer, jockey, the two together, the trainer at the course, the sire and the horse, over 90- and 365-day half-lives and the career; the horse's pounds-beaten volatility, downside deviation, best, drawdown and runs since the best, and the market's volatility and trend on it. Lag, card, order and READS tests pass. Iteration 106 (served recipe): the served main with the block, and with its record half only.</t>
+    <t xml:space="preserve">Built 30 Sep at the owner's ask (measures from the financial markets): the Sharpe ratio of level-stake returns at the Betfair SP, the signed chi (z-score) of winners against the prices' expectation and A/E for the trainer, jockey, the two together, the trainer at the course, the sire and the horse, over 90- and 365-day half-lives and the career; the horse's pounds-beaten volatility, downside deviation, best, drawdown and runs since the best, and the market's volatility and trend on it. Lag, card, order and READS tests pass. Iteration 106 (served recipe, 53,910 runners in 5,923 races): the served main with the block +0.0001 (-0.0005 to +0.0008), with its record half only +0.0002 (-0.0004 to +0.0009), Brier skill and concordance level; the rule +10.50% and +10.69% against +10.38%; the owner's staking at expected CLV &gt;= 3% +6.62% and +6.30% against +6.11% (held +4.12% and +1.78% against +3.88%), at &gt;= 0% +3.94% and +4.24% against +4.23%: all inside the noise. Retired.</t>
   </si>
   <si>
     <t xml:space="preserve">Iteration 35: -0.0004; iteration 54 (steadier screen): -0.0009 (-0.0023 to +0.0003): nothing.</t>

--- a/reports/feature_inventory.xlsx
+++ b/reports/feature_inventory.xlsx
@@ -10180,10 +10180,10 @@
     <t xml:space="preserve">The owner's formula (6 Oct): on 54,151 GB/IE races from 2022 to Mar 2026 it predicted the winner a little better than the engine's NFP over every window, +0.55 to +0.93 millinats a race on its own (research/queries/done/nfp_formula_check.py, capped at the holdout's start), and like it adds nothing beside the BSP. Iteration 108 (served recipe, 53,910 runners in 5,923 races): the served main with the block +0.0002 (-0.0004 to +0.0008), Brier skill and concordance level, the rule +9.03% against +9.04%, the owner's staking at expected CLV &gt;= 3% +6.53% against +6.50%. Retired.</t>
   </si>
   <si>
-    <t xml:space="preserve">Built 6 Oct from the owner's horseracebase list (reports/hrb_system_builder_review.md). On 54,151 GB/IE races from 2022 to Mar 2026 (research/queries/done/hrb_features_screen.py) 84.8% of runs have a price-file record. On the winner alone the block scores +137 millinats a race (t 61), the last five weighted low +112: it reads form as the market saw it run. Beside the BSP it adds nothing (-0.69, t -1.6), and A/E by the last run's in-running low runs 0.97-1.01: the market already prices a horse that traded short and was beaten. Iteration 109 puts it in front of the served model, which forecasts the BSP. Not served.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built 6 Oct from the owner's horseracebase list. Beside the BSP on the winner, the same screen: same surname +0.01 (t 0.5; 1.9% of runners, winning 14.1% against the market's 13.7%), seconds ~0, the last race's winner's BSP -0.06, its non-finishers -0.04, the biggest field won in -0.33 (t -5.0), last year's run at the course and trip -0.18 (t -2.5); together -0.65 (t -4.8). Iteration 109 puts it in front of the served model. Not served.</t>
+    <t xml:space="preserve">Built 6 Oct from the owner's horseracebase list (reports/hrb_system_builder_review.md). On 54,151 GB/IE races from 2022 to Mar 2026 (research/queries/done/hrb_features_screen.py) 84.8% of runs have a price-file record. On the winner alone the block scores +137 millinats a race (t 61), the last five weighted low +112: it reads form as the market saw it run. Beside the BSP it adds nothing (-0.69, t -1.6), and A/E by the last run's in-running low runs 0.97-1.01: the market already prices a horse that traded short and was beaten. Iteration 109 (served recipe, 53,910 runners in 5,923 races): the served main with the block -0.0008 (-0.0014 to -0.0002), resolved, rank 1 -0.0020 (-0.0030 to -0.0010), Brier skill and concordance level, the rule +9.07% against +9.04%, the owner's staking at expected CLV &gt;= 3% +6.88% against +6.50%. Iteration 110 tries it in every member of the served blend and at seed 7. Not yet served.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 6 Oct from the owner's horseracebase list. Beside the BSP on the winner, the same screen: same surname +0.01 (t 0.5; 1.9% of runners, winning 14.1% against the market's 13.7%), seconds ~0, the last race's winner's BSP -0.06, its non-finishers -0.04, the biggest field won in -0.33 (t -5.0), last year's run at the course and trip -0.18 (t -2.5); together -0.65 (t -4.8). Iteration 109: the served main with the block +0.0001 (-0.0004 to +0.0007), Brier skill and concordance level, the owner's staking at &gt;= 3% +6.66% against +6.50%. Retired.</t>
   </si>
   <si>
     <t xml:space="preserve">Iteration 35: -0.0004; iteration 54 (steadier screen): -0.0009 (-0.0023 to +0.0003): nothing.</t>

--- a/reports/feature_inventory.xlsx
+++ b/reports/feature_inventory.xlsx
@@ -10180,7 +10180,7 @@
     <t xml:space="preserve">The owner's formula (6 Oct): on 54,151 GB/IE races from 2022 to Mar 2026 it predicted the winner a little better than the engine's NFP over every window, +0.55 to +0.93 millinats a race on its own (research/queries/done/nfp_formula_check.py, capped at the holdout's start), and like it adds nothing beside the BSP. Iteration 108 (served recipe, 53,910 runners in 5,923 races): the served main with the block +0.0002 (-0.0004 to +0.0008), Brier skill and concordance level, the rule +9.03% against +9.04%, the owner's staking at expected CLV &gt;= 3% +6.53% against +6.50%. Retired.</t>
   </si>
   <si>
-    <t xml:space="preserve">Built 6 Oct from the owner's horseracebase list (reports/hrb_system_builder_review.md). On 54,151 GB/IE races from 2022 to Mar 2026 (research/queries/done/hrb_features_screen.py) 84.8% of runs have a price-file record. On the winner alone the block scores +137 millinats a race (t 61), the last five weighted low +112: it reads form as the market saw it run. Beside the BSP it adds nothing (-0.69, t -1.6), and A/E by the last run's in-running low runs 0.97-1.01: the market already prices a horse that traded short and was beaten. Iteration 109 (served recipe, 53,910 runners in 5,923 races): the served main with the block -0.0008 (-0.0014 to -0.0002), resolved, rank 1 -0.0020 (-0.0030 to -0.0010), Brier skill and concordance level, the rule +9.07% against +9.04%, the owner's staking at expected CLV &gt;= 3% +6.88% against +6.50%. Iteration 110 tries it in every member of the served blend and at seed 7. Not yet served.</t>
+    <t xml:space="preserve">Built 6 Oct from the owner's horseracebase list (reports/hrb_system_builder_review.md). On 54,151 GB/IE races from 2022 to Mar 2026 (research/queries/done/hrb_features_screen.py) 84.8% of runs have a price-file record. On the winner alone the block scores +137 millinats a race (t 61), the last five weighted low +112: it reads form as the market saw it run. Beside the BSP it adds nothing (-0.69, t -1.6), and A/E by the last run's in-running low runs 0.97-1.01: the market already prices a horse that traded short and was beaten. Iteration 109 (served recipe, 53,910 runners in 5,923 races): the served main with the block -0.0008 (-0.0014 to -0.0002), resolved, rank 1 -0.0020 (-0.0030 to -0.0010), Brier skill and concordance level, the rule +9.07% against +9.04%, the owner's staking at expected CLV &gt;= 3% +6.88% against +6.50%. Iteration 110 (research loop run 37532787409): the main with the block -0.0007 again (-0.0013 to -0.0001), but at seed 7 -0.0005 on its own refit (-0.0011 to +0.0001) with Brier skill against the market resolved worse (-0.00066); in the served blend, all three members with the block against the blend refitted -0.0003 (-0.0008 to +0.0002), race_xent only -0.0002, the pair only -0.0002, none resolved (research/queries/done/iter110_gate_pairwise.py); the owner's staking +7.74% against +7.67%. Built, not served.</t>
   </si>
   <si>
     <t xml:space="preserve">Built 6 Oct from the owner's horseracebase list. Beside the BSP on the winner, the same screen: same surname +0.01 (t 0.5; 1.9% of runners, winning 14.1% against the market's 13.7%), seconds ~0, the last race's winner's BSP -0.06, its non-finishers -0.04, the biggest field won in -0.33 (t -5.0), last year's run at the course and trip -0.18 (t -2.5); together -0.65 (t -4.8). Iteration 109: the served main with the block +0.0001 (-0.0004 to +0.0007), Brier skill and concordance level, the owner's staking at &gt;= 3% +6.66% against +6.50%. Retired.</t>
